--- a/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/mrt_cp_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1258271604938271</v>
+        <v>0.1282273860398861</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -479,16 +479,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.95</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02776643759450143</v>
+        <v>0.0277296776935901</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8294642857142857</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="H2" t="n">
-        <v>1.071428571428571</v>
+        <v>1.176470588235294</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06395061728395063</v>
+        <v>0.05827362996480642</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9142857142857143</v>
+        <v>1.041176470588235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0245134050975881</v>
+        <v>0.06203643929237794</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8294642857142857</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="H3" t="n">
-        <v>1.075</v>
+        <v>1.372058823529412</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06196825396825395</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.9941176470588236</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02332847374079217</v>
+        <v>0.04423731048109208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8017857142857142</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="H4" t="n">
-        <v>1.047321428571429</v>
+        <v>1.222058823529412</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.06134920634920635</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3928571428571428</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9178571428571427</v>
+        <v>1.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02383926713631046</v>
+        <v>0.01999615495526582</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8017857142857142</v>
+        <v>1.085294117647059</v>
       </c>
       <c r="H5" t="n">
-        <v>1.047321428571429</v>
+        <v>1.280882352941177</v>
       </c>
     </row>
     <row r="6">
@@ -574,25 +574,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02777777777777777</v>
+        <v>0.03676470588235292</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8892857142857142</v>
+        <v>1.211764705882353</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02789374884252377</v>
+        <v>0.02183437005031381</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7303571428571428</v>
+        <v>1.085294117647059</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9919642857142857</v>
+        <v>1.294117647058824</v>
       </c>
     </row>
     <row r="7">
@@ -600,25 +600,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01777777777777778</v>
+        <v>0.02638888888888891</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9178571428571429</v>
+        <v>1.264705882352941</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02556060780188559</v>
+        <v>0.0280741589476007</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8214285714285714</v>
+        <v>1.130882352941176</v>
       </c>
       <c r="H7" t="n">
-        <v>1.027678571428571</v>
+        <v>1.398529411764706</v>
       </c>
     </row>
     <row r="8">
@@ -626,25 +626,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01728395061728395</v>
+        <v>0.02430555555555555</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9178571428571429</v>
+        <v>1.264705882352941</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02556060780188559</v>
+        <v>0.0280741589476007</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8214285714285714</v>
+        <v>1.130882352941176</v>
       </c>
       <c r="H8" t="n">
-        <v>1.027678571428571</v>
+        <v>1.398529411764706</v>
       </c>
     </row>
     <row r="9">
@@ -652,25 +652,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01481481481481482</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9428571428571428</v>
+        <v>1.264705882352941</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02725124557680857</v>
+        <v>0.0280741589476007</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8294642857142857</v>
+        <v>1.130882352941176</v>
       </c>
       <c r="H9" t="n">
-        <v>1.083035714285714</v>
+        <v>1.398529411764706</v>
       </c>
     </row>
     <row r="10">
@@ -678,51 +678,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2142857142857143</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9535714285714285</v>
+        <v>1.258823529411765</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02717312431074602</v>
+        <v>0.02934633244528582</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8571428571428571</v>
+        <v>1.117647058823529</v>
       </c>
       <c r="H10" t="n">
-        <v>1.110714285714286</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.9535714285714285</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.02717312431074602</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.110714285714286</v>
+        <v>1.398529411764706</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelB_CorePeripheral/tables/mrt_cp_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,25 +522,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9941176470588236</v>
+        <v>1.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04423731048109208</v>
+        <v>0.01999615495526582</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8235294117647058</v>
+        <v>1.085294117647059</v>
       </c>
       <c r="H4" t="n">
-        <v>1.222058823529412</v>
+        <v>1.280882352941177</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.03676470588235292</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>1.211764705882353</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01999615495526582</v>
+        <v>0.02183437005031381</v>
       </c>
       <c r="G5" t="n">
         <v>1.085294117647059</v>
       </c>
       <c r="H5" t="n">
-        <v>1.280882352941177</v>
+        <v>1.294117647058824</v>
       </c>
     </row>
     <row r="6">
@@ -574,25 +574,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03676470588235292</v>
+        <v>0.02638888888888891</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0.4117647058823529</v>
       </c>
       <c r="E6" t="n">
-        <v>1.211764705882353</v>
+        <v>1.264705882352941</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02183437005031381</v>
+        <v>0.0280741589476007</v>
       </c>
       <c r="G6" t="n">
-        <v>1.085294117647059</v>
+        <v>1.130882352941176</v>
       </c>
       <c r="H6" t="n">
-        <v>1.294117647058824</v>
+        <v>1.398529411764706</v>
       </c>
     </row>
     <row r="7">
@@ -600,13 +600,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02638888888888891</v>
+        <v>0.02430555555555555</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="E7" t="n">
         <v>1.264705882352941</v>
@@ -626,13 +626,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02430555555555555</v>
+        <v>0.02222222222222222</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="E8" t="n">
         <v>1.264705882352941</v>
@@ -652,50 +652,24 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02222222222222222</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="E9" t="n">
-        <v>1.264705882352941</v>
+        <v>1.258823529411765</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0280741589476007</v>
+        <v>0.02934633244528582</v>
       </c>
       <c r="G9" t="n">
-        <v>1.130882352941176</v>
+        <v>1.117647058823529</v>
       </c>
       <c r="H9" t="n">
-        <v>1.398529411764706</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>9</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.258823529411765</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.02934633244528582</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.117647058823529</v>
-      </c>
-      <c r="H10" t="n">
         <v>1.398529411764706</v>
       </c>
     </row>
